--- a/AI-Agent-学习追踪表.xlsx
+++ b/AI-Agent-学习追踪表.xlsx
@@ -704,14 +704,14 @@
         <v>8</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
@@ -1245,11 +1245,15 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
+      <c r="F3" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
       <c r="G3" s="30" t="n"/>
       <c r="H3" s="31" t="n"/>
     </row>
